--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EDB9E05-506D-47A5-A30E-62C793C11CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFEBC83-8379-4C21-BAF8-EE0A0C97EDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>Augest</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>revised the topics coverd during the weeks</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1048,9 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
+      <c r="A7" s="13">
+        <v>46255</v>
+      </c>
       <c r="B7" s="14">
         <v>360</v>
       </c>
@@ -1082,27 +1093,51 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>420</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFEBC83-8379-4C21-BAF8-EE0A0C97EDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F491F7B4-B6A4-4ABD-9D1A-BB883ADFC468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>revised the topics coverd during the weeks</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>it was productive Sunday</t>
   </si>
 </sst>
 </file>
@@ -1140,26 +1146,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>360</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F491F7B4-B6A4-4ABD-9D1A-BB883ADFC468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B2C3A2-4604-4D8B-81C6-31A1BA152CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>it was productive Sunday</t>
+  </si>
+  <si>
+    <t>today I learned python syntax variables, string</t>
   </si>
 </sst>
 </file>
@@ -1191,27 +1194,51 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B10" s="14">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>30</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>350</v>
+      </c>
+      <c r="G10" s="14">
+        <v>7</v>
+      </c>
+      <c r="H10" s="14">
+        <v>360</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B2C3A2-4604-4D8B-81C6-31A1BA152CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C7D5F1-D16D-49D5-84EF-5D8DF03F7217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>today I learned python syntax variables, string</t>
+  </si>
+  <si>
+    <t>25-082026</t>
+  </si>
+  <si>
+    <t>learning python today</t>
   </si>
 </sst>
 </file>
@@ -1241,26 +1247,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="14">
+        <v>300</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>30</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>300</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C7D5F1-D16D-49D5-84EF-5D8DF03F7217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D46E3D0-81F1-440A-A8C3-69E8C60BCFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>learning python today</t>
+  </si>
+  <si>
+    <t>today I slove one two python problems</t>
   </si>
 </sst>
 </file>
@@ -1292,27 +1295,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>30</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>360</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D46E3D0-81F1-440A-A8C3-69E8C60BCFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA82367-84A1-4E09-BF2D-7EBD632A116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>today I slove one two python problems</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>today i learned python functions</t>
   </si>
 </sst>
 </file>
@@ -1342,26 +1348,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>150</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3</v>
+      </c>
+      <c r="H13" s="14">
+        <v>360</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA82367-84A1-4E09-BF2D-7EBD632A116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CBFF72-AECD-4B56-AA1B-28B0B49FAE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -234,9 +234,6 @@
     <t>today I learned python syntax variables, string</t>
   </si>
   <si>
-    <t>25-082026</t>
-  </si>
-  <si>
     <t>learning python today</t>
   </si>
   <si>
@@ -247,6 +244,9 @@
   </si>
   <si>
     <t>today i learned python functions</t>
+  </si>
+  <si>
+    <t>today i learn more about python</t>
   </si>
 </sst>
 </file>
@@ -1256,8 +1256,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>65</v>
+      <c r="A11" s="13">
+        <v>46259</v>
       </c>
       <c r="B11" s="14">
         <v>300</v>
@@ -1298,7 +1298,7 @@
         <v>60</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1344,7 +1344,7 @@
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1381,7 +1381,7 @@
         <v>510</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>62</v>
@@ -1390,30 +1390,54 @@
         <v>60</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>30</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>420</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CBFF72-AECD-4B56-AA1B-28B0B49FAE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090836BE-BC90-4FC4-BFB7-80FCB3A79A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>today i learn more about python</t>
+  </si>
+  <si>
+    <t>`0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I will pratice every day </t>
   </si>
 </sst>
 </file>
@@ -1440,26 +1446,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="14">
+        <v>360</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090836BE-BC90-4FC4-BFB7-80FCB3A79A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C417C41-5659-42A2-9AA8-B5D68019C451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,9 +240,6 @@
     <t>today I slove one two python problems</t>
   </si>
   <si>
-    <t>Stressed</t>
-  </si>
-  <si>
     <t>today i learned python functions</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t xml:space="preserve">I will pratice every day </t>
+  </si>
+  <si>
+    <t>Good Progrress today;will focus more on coding tomorrow</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1387,7 @@
         <v>510</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>62</v>
@@ -1396,7 +1396,7 @@
         <v>60</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1442,7 +1442,7 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H15" s="14">
         <v>360</v>
@@ -1488,30 +1488,54 @@
         <v>60</v>
       </c>
       <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>30</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>350</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>360</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C417C41-5659-42A2-9AA8-B5D68019C451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7C3500-C3CF-4EAD-8468-9E0FD7BAD52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Good Progrress today;will focus more on coding tomorrow</t>
+  </si>
+  <si>
+    <t>today I learn some classes</t>
   </si>
 </sst>
 </file>
@@ -1538,26 +1541,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>400</v>
+      </c>
+      <c r="G17" s="14">
+        <v>8</v>
+      </c>
+      <c r="H17" s="14">
+        <v>360</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7C3500-C3CF-4EAD-8468-9E0FD7BAD52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62BDE65-4FCE-4B38-89A3-3A7EBF1121E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>today I learn some classes</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>get  confused in logic building</t>
   </si>
 </sst>
 </file>
@@ -1587,26 +1593,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>30</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>350</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>360</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62BDE65-4FCE-4B38-89A3-3A7EBF1121E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA59C076-0382-4E22-BEFE-1559D9F18A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1639,26 +1639,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>150</v>
+      </c>
+      <c r="G19" s="14">
+        <v>3</v>
+      </c>
+      <c r="H19" s="14">
+        <v>530</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA59C076-0382-4E22-BEFE-1559D9F18A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD112F5-2A11-4798-B8B7-04636D578E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>get  confused in logic building</t>
+  </si>
+  <si>
+    <t>Today, I studied networking for the CA.</t>
+  </si>
+  <si>
+    <t>yesterday I was travelling, so I couldn’t write anything.</t>
   </si>
 </sst>
 </file>
@@ -1684,49 +1690,97 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>30</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>150</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>420</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>150</v>
+      </c>
+      <c r="E21" s="14">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>360</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>973</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>467</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
